--- a/project/table_tools/table/SummonData.xlsx
+++ b/project/table_tools/table/SummonData.xlsx
@@ -1,33 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyGitHub\DrawAvatar\table\client\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CFDFE0-1E33-4389-B078-9926691758BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SummonData" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="101">
   <si>
     <t>序号</t>
   </si>
@@ -94,9 +87,6 @@
     <t>commandStrs</t>
   </si>
   <si>
-    <t>associateCompType</t>
-  </si>
-  <si>
     <t>enableSetting</t>
   </si>
   <si>
@@ -117,9 +107,6 @@
   </si>
   <si>
     <t>0，无； 1，单位； 2，天帝令</t>
-  </si>
-  <si>
-    <t>1,红 ；2，蓝色</t>
   </si>
   <si>
     <t>主要针对礼物：是否把该礼物放入设置界面，允许主播开启或者该礼物特效</t>
@@ -188,9 +175,6 @@
     <t>红色仙女棒</t>
   </si>
   <si>
-    <t>1;2</t>
-  </si>
-  <si>
     <t>true</t>
   </si>
   <si>
@@ -360,9 +344,6 @@
     <t>红,1</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -370,9 +351,6 @@
   </si>
   <si>
     <t>蓝,2</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>1003</t>
@@ -432,15 +410,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,151 +466,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -661,188 +497,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -880,251 +536,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1150,7 +564,7 @@
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1162,16 +576,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
@@ -1235,58 +649,80 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1302,6 +738,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1559,27 +998,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.25" style="3" customWidth="1"/>
     <col min="2" max="2" width="27.875" style="4" customWidth="1"/>
     <col min="3" max="3" width="13.875" style="4" customWidth="1"/>
     <col min="4" max="5" width="42.875" style="4" customWidth="1"/>
-    <col min="6" max="7" width="19" style="5" customWidth="1"/>
-    <col min="8" max="9" width="19" style="4" customWidth="1"/>
-    <col min="10" max="10" width="31.75" style="4" customWidth="1"/>
-    <col min="11" max="11" width="26.5" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="4"/>
+    <col min="6" max="6" width="19" style="5" customWidth="1"/>
+    <col min="7" max="8" width="19" style="4" customWidth="1"/>
+    <col min="9" max="9" width="31.75" style="4" customWidth="1"/>
+    <col min="10" max="10" width="26.5" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1596,24 +1035,23 @@
       <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="H1" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
@@ -1644,76 +1082,67 @@
       <c r="J2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" ht="108.75" customHeight="1" spans="1:12">
+    </row>
+    <row r="3" spans="1:11" ht="108.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
       <c r="D3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="J3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="11" t="s">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A4" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="8" t="s">
-        <v>29</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="G4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="11" t="s">
+      <c r="H4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A5" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="12" t="s">
-        <v>34</v>
       </c>
       <c r="B5" s="9">
         <v>3</v>
@@ -1722,22 +1151,21 @@
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="G5" s="14"/>
       <c r="H5" s="14"/>
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="4">
+      <c r="K5" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:12">
+    <row r="6" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A6" s="15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6" s="18">
         <v>100</v>
@@ -1746,29 +1174,26 @@
         <v>1</v>
       </c>
       <c r="F6" s="19"/>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="J6" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="21" t="s">
+    </row>
+    <row r="7" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="15" t="s">
         <v>39</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6" s="19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:12">
-      <c r="A7" s="15" t="s">
-        <v>42</v>
       </c>
       <c r="B7" s="16"/>
       <c r="C7" s="17" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D7" s="18">
         <v>100</v>
@@ -1777,29 +1202,26 @@
         <v>1</v>
       </c>
       <c r="F7" s="19"/>
-      <c r="G7" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>38</v>
+      <c r="G7" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>41</v>
       </c>
       <c r="I7" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="J7" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:12">
-      <c r="A8" s="15" t="s">
-        <v>47</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="17" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D8" s="18">
         <v>100</v>
@@ -1808,29 +1230,26 @@
         <v>1</v>
       </c>
       <c r="F8" s="19"/>
-      <c r="G8" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>38</v>
+      <c r="G8" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="I8" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="15" t="s">
         <v>49</v>
-      </c>
-      <c r="J8" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="K8" s="19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:12">
-      <c r="A9" s="15" t="s">
-        <v>52</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="17" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D9" s="18">
         <v>100</v>
@@ -1839,29 +1258,26 @@
         <v>1</v>
       </c>
       <c r="F9" s="19"/>
-      <c r="G9" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>38</v>
+      <c r="G9" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>51</v>
       </c>
       <c r="I9" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="15" t="s">
         <v>54</v>
-      </c>
-      <c r="J9" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:12">
-      <c r="A10" s="15" t="s">
-        <v>57</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="22" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D10" s="18">
         <v>100</v>
@@ -1870,29 +1286,26 @@
         <v>1</v>
       </c>
       <c r="F10" s="19"/>
-      <c r="G10" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>38</v>
+      <c r="G10" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>56</v>
       </c>
       <c r="I10" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="15" t="s">
         <v>59</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="K10" s="19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:12">
-      <c r="A11" s="15" t="s">
-        <v>62</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D11" s="18">
         <v>100</v>
@@ -1901,29 +1314,26 @@
         <v>1</v>
       </c>
       <c r="F11" s="19"/>
-      <c r="G11" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>38</v>
+      <c r="G11" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>61</v>
       </c>
       <c r="I11" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="1" customFormat="1" ht="33" x14ac:dyDescent="0.15">
+      <c r="A12" s="15" t="s">
         <v>64</v>
-      </c>
-      <c r="J11" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="33" spans="1:12">
-      <c r="A12" s="15" t="s">
-        <v>67</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D12" s="18">
         <v>100</v>
@@ -1932,29 +1342,26 @@
         <v>1</v>
       </c>
       <c r="F12" s="19"/>
-      <c r="G12" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>38</v>
+      <c r="G12" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>66</v>
       </c>
       <c r="I12" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="15" t="s">
         <v>69</v>
-      </c>
-      <c r="J12" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="K12" s="19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:12">
-      <c r="A13" s="15" t="s">
-        <v>72</v>
       </c>
       <c r="B13" s="23"/>
       <c r="C13" s="17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D13" s="18">
         <v>100</v>
@@ -1963,26 +1370,23 @@
         <v>2</v>
       </c>
       <c r="F13" s="19"/>
-      <c r="G13" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>38</v>
+      <c r="G13" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="I13" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13" s="19"/>
+    </row>
+    <row r="14" spans="1:11" s="2" customFormat="1" ht="24" x14ac:dyDescent="0.15">
+      <c r="A14" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="25" t="s">
         <v>74</v>
-      </c>
-      <c r="J13" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="K13" s="19"/>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="24" spans="1:12">
-      <c r="A14" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>77</v>
       </c>
       <c r="C14" s="26"/>
       <c r="D14" s="27">
@@ -1990,26 +1394,23 @@
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="28"/>
-      <c r="G14" s="20" t="s">
-        <v>37</v>
+      <c r="G14" s="28" t="s">
+        <v>75</v>
       </c>
       <c r="H14" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="29"/>
+      <c r="J14" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A15" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="31" t="s">
         <v>78</v>
-      </c>
-      <c r="I14" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="J14" s="29"/>
-      <c r="K14" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>81</v>
       </c>
       <c r="C15" s="31"/>
       <c r="D15" s="31">
@@ -2017,26 +1418,23 @@
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>83</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="G15" s="20"/>
       <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="K15" s="33">
+      <c r="I15" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="30" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C16" s="31"/>
       <c r="D16" s="31">
@@ -2044,22 +1442,19 @@
       </c>
       <c r="E16" s="31"/>
       <c r="F16" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>87</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="G16" s="20"/>
       <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="33"/>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="I16" s="32"/>
+      <c r="J16" s="33"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" s="30" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C17" s="31"/>
       <c r="D17" s="31">
@@ -2067,22 +1462,19 @@
       </c>
       <c r="E17" s="31"/>
       <c r="F17" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>37</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="G17" s="20"/>
       <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="33"/>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="I17" s="32"/>
+      <c r="J17" s="33"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" s="30" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C18" s="31"/>
       <c r="D18" s="31">
@@ -2090,26 +1482,23 @@
       </c>
       <c r="E18" s="31"/>
       <c r="F18" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>37</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="G18" s="20"/>
       <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="K18" s="33">
+      <c r="I18" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="J18" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" s="30" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C19" s="31"/>
       <c r="D19" s="31">
@@ -2117,100 +1506,88 @@
       </c>
       <c r="E19" s="31"/>
       <c r="F19" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>37</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="G19" s="20"/>
       <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="K19" s="33">
+      <c r="I19" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="J19" s="33">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" s="30" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D20" s="4">
         <v>4</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J20" s="34"/>
-    </row>
-    <row r="21" spans="1:11">
+        <v>94</v>
+      </c>
+      <c r="I20" s="34"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" s="30" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D21" s="4">
         <v>5</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J21" s="34"/>
-    </row>
-    <row r="22" spans="1:11">
+        <v>97</v>
+      </c>
+      <c r="I21" s="34"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D22" s="4">
         <v>6</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="B7:B8">
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="duplicateValues" dxfId="6" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14 B11:C13">
+    <cfRule type="duplicateValues" dxfId="5" priority="31"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B6:C6">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C9">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  <conditionalFormatting sqref="C7:C8">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
     <cfRule type="duplicateValues" dxfId="0" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B8">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7:C8">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14 B11:C13">
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>